--- a/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T10:50:27+00:00</t>
+    <t>2026-04-07T13:39:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T13:39:53+00:00</t>
+    <t>2026-04-08T09:43:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T09:43:36+00:00</t>
+    <t>2026-04-08T13:03:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T13:03:38+00:00</t>
+    <t>2026-04-08T14:07:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-accession-number-identifier-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
